--- a/Web/TestCasesWeb/Dispositivos.xlsx
+++ b/Web/TestCasesWeb/Dispositivos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA8CE3B-C244-4BA6-9234-F4FB881B4E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Web/TestCasesWeb/Dispositivos.xlsx
+++ b/Web/TestCasesWeb/Dispositivos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA8CE3B-C244-4BA6-9234-F4FB881B4E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7795197-CE80-44E2-A0A7-AB2E9F21394A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Num</t>
   </si>
@@ -74,19 +74,16 @@
   </si>
   <si>
     <t>1. Devices' list are updated.</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>No hay datos que poder comprobar</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks "Dispositivos"
 </t>
   </si>
   <si>
-    <t>1. The user selects restaurants</t>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant</t>
   </si>
 </sst>
 </file>
@@ -561,18 +558,18 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
@@ -585,14 +582,16 @@
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -612,9 +611,11 @@
       <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3"/>
     </row>

--- a/Web/TestCasesWeb/Dispositivos.xlsx
+++ b/Web/TestCasesWeb/Dispositivos.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7795197-CE80-44E2-A0A7-AB2E9F21394A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A2565-A76E-4817-814C-EBA657250DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Web/TestCasesWeb/Dispositivos.xlsx
+++ b/Web/TestCasesWeb/Dispositivos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A2565-A76E-4817-814C-EBA657250DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF37735-E169-47D1-BEE6-C874A51015C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="0" windowWidth="23265" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>Num</t>
   </si>
@@ -59,12 +59,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Devices page home</t>
-  </si>
-  <si>
-    <t>1. Devices page home is correctly.</t>
-  </si>
-  <si>
     <t>DEV001</t>
   </si>
   <si>
@@ -74,16 +68,7 @@
     <t>DEV003</t>
   </si>
   <si>
-    <t>Connected device</t>
-  </si>
-  <si>
     <t>1. The connected device is shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update device </t>
-  </si>
-  <si>
-    <t>1. The user clicks "Actualizar dispositivos"</t>
   </si>
   <si>
     <t>1. Devices' list are updated.</t>
@@ -96,14 +81,50 @@
     <t>OK</t>
   </si>
   <si>
-    <t>1. The user selects a restaurant</t>
+    <t>Devices page</t>
+  </si>
+  <si>
+    <t>Devices: Connected</t>
+  </si>
+  <si>
+    <t>Devices: Update</t>
+  </si>
+  <si>
+    <t>1. Devices page is correctly.</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>No tiene sentido tener dos combox de restaurantes: DEV001.jpg</t>
+  </si>
+  <si>
+    <t>Devices: Disconnected</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant
+(there is a device connected)</t>
+  </si>
+  <si>
+    <t>1. The connected device is not shown.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Actualizar dispositivos"
+(The devices are connected and disconnected)</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant
+(There are no connected device)</t>
+  </si>
+  <si>
+    <t>DEV004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +146,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -165,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -184,6 +212,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -565,76 +596,102 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="7" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -649,5 +706,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>